--- a/diseases/d105/2000-2004.xlsx
+++ b/diseases/d105/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>7</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.1352343026058781</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>1.066552901023891</v>
       </c>
@@ -1853,9 +1847,6 @@
       <c r="O8" t="n">
         <v>9</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2004067366056487</v>
       </c>
@@ -2397,9 +2388,6 @@
       <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -2941,9 +2929,6 @@
       <c r="O14" t="n">
         <v>11</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -3485,9 +3470,6 @@
       <c r="O17" t="n">
         <v>4</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.07727674434621605</v>
       </c>
@@ -4029,9 +4011,6 @@
       <c r="O20" t="n">
         <v>11</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -4573,9 +4552,6 @@
       <c r="O23" t="n">
         <v>6</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -5117,9 +5093,6 @@
       <c r="O26" t="n">
         <v>11</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -5661,9 +5634,6 @@
       <c r="O29" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.1931918608655401</v>
       </c>
@@ -6205,9 +6175,6 @@
       <c r="O32" t="n">
         <v>19</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.4230808883897029</v>
       </c>
@@ -6749,9 +6716,6 @@
       <c r="O35" t="n">
         <v>2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -7293,9 +7257,6 @@
       <c r="O38" t="n">
         <v>4</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -7837,9 +7798,6 @@
       <c r="O41" t="n">
         <v>2</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.03863837217310803</v>
       </c>
@@ -8381,9 +8339,6 @@
       <c r="O44" t="n">
         <v>12</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.267208982140865</v>
       </c>
@@ -8925,9 +8880,6 @@
       <c r="O47" t="n">
         <v>8</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1545534886924321</v>
       </c>
@@ -9469,9 +9421,6 @@
       <c r="O50" t="n">
         <v>16</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -10013,9 +9962,6 @@
       <c r="O53" t="n">
         <v>6</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.1159151165193241</v>
       </c>
@@ -10557,9 +10503,6 @@
       <c r="O56" t="n">
         <v>16</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.3562786428544867</v>
       </c>
@@ -11101,9 +11044,6 @@
       <c r="O59" t="n">
         <v>11</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.2125110469520941</v>
       </c>
@@ -11645,9 +11585,6 @@
       <c r="O62" t="n">
         <v>6</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -12189,9 +12126,6 @@
       <c r="O65" t="n">
         <v>13</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.2511494191252021</v>
       </c>
@@ -12733,9 +12667,6 @@
       <c r="O68" t="n">
         <v>11</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.2449415669624596</v>
       </c>
@@ -13277,9 +13208,6 @@
       <c r="O71" t="n">
         <v>9</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.1738726747789861</v>
       </c>
@@ -13821,9 +13749,6 @@
       <c r="O74" t="n">
         <v>10</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.2226741517840542</v>
       </c>
@@ -14365,9 +14290,6 @@
       <c r="O77" t="n">
         <v>20</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.3855071664818481</v>
       </c>
@@ -14909,9 +14831,6 @@
       <c r="O80" t="n">
         <v>2</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.7016251392287386</v>
       </c>
@@ -15305,9 +15224,6 @@
       <c r="O82" t="n">
         <v>6</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01275416174674877</v>
       </c>
@@ -15453,9 +15369,6 @@
       <c r="O83" t="n">
         <v>11</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.2437048273716855</v>
       </c>
@@ -15997,9 +15910,6 @@
       <c r="O86" t="n">
         <v>21</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.4047825248059406</v>
       </c>
@@ -16541,9 +16451,6 @@
       <c r="O89" t="n">
         <v>56</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.1190388429696552</v>
       </c>
@@ -16689,9 +16596,6 @@
       <c r="O90" t="n">
         <v>17</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -17233,9 +17137,6 @@
       <c r="O93" t="n">
         <v>17</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.3276810915095709</v>
       </c>
@@ -17777,9 +17678,6 @@
       <c r="O96" t="n">
         <v>66</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.1402957792142365</v>
       </c>
@@ -17925,9 +17823,6 @@
       <c r="O97" t="n">
         <v>12</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -18469,9 +18364,6 @@
       <c r="O100" t="n">
         <v>10</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.1927535832409241</v>
       </c>
@@ -19013,9 +18905,6 @@
       <c r="O103" t="n">
         <v>25</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.05314234061145322</v>
       </c>
@@ -19161,9 +19050,6 @@
       <c r="O104" t="n">
         <v>23</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.5095646390498879</v>
       </c>
@@ -19705,9 +19591,6 @@
       <c r="O107" t="n">
         <v>11</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.2120289415650165</v>
       </c>
@@ -20249,9 +20132,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -20397,9 +20277,6 @@
       <c r="O111" t="n">
         <v>18</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -20941,9 +20818,6 @@
       <c r="O114" t="n">
         <v>7</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.1349275082686468</v>
       </c>
@@ -21485,9 +21359,6 @@
       <c r="O117" t="n">
         <v>9</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.01913124262012316</v>
       </c>
@@ -21633,9 +21504,6 @@
       <c r="O118" t="n">
         <v>10</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -22177,9 +22045,6 @@
       <c r="O121" t="n">
         <v>17</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.3276810915095709</v>
       </c>
@@ -22721,9 +22586,6 @@
       <c r="O124" t="n">
         <v>3</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.006377080873374387</v>
       </c>
@@ -22869,9 +22731,6 @@
       <c r="O125" t="n">
         <v>18</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.3987897175173036</v>
       </c>
@@ -23413,9 +23272,6 @@
       <c r="O128" t="n">
         <v>38</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.7324636163155114</v>
       </c>
@@ -23957,9 +23813,6 @@
       <c r="O131" t="n">
         <v>4</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.008502774497832516</v>
       </c>
@@ -24105,9 +23958,6 @@
       <c r="O132" t="n">
         <v>19</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.4209447018238204</v>
       </c>
@@ -24649,9 +24499,6 @@
       <c r="O135" t="n">
         <v>50</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.9637679162046202</v>
       </c>
@@ -25193,9 +25040,6 @@
       <c r="O138" t="n">
         <v>12</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.02550832349349755</v>
       </c>
@@ -25341,9 +25185,6 @@
       <c r="O139" t="n">
         <v>32</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.7089594978085397</v>
       </c>
@@ -25885,9 +25726,6 @@
       <c r="O142" t="n">
         <v>22</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.424057883130033</v>
       </c>
@@ -26429,9 +26267,6 @@
       <c r="O145" t="n">
         <v>16</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.03401109799133006</v>
       </c>
@@ -26577,9 +26412,6 @@
       <c r="O146" t="n">
         <v>15</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.332324764597753</v>
       </c>
@@ -27121,9 +26953,6 @@
       <c r="O149" t="n">
         <v>15</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.289130374861386</v>
       </c>
@@ -27665,9 +27494,6 @@
       <c r="O152" t="n">
         <v>56</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.1190388429696552</v>
       </c>
@@ -27813,9 +27639,6 @@
       <c r="O153" t="n">
         <v>10</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -28357,9 +28180,6 @@
       <c r="O156" t="n">
         <v>4</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.07710143329636962</v>
       </c>
@@ -28901,9 +28721,6 @@
       <c r="O159" t="n">
         <v>671</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>1.426340422011404</v>
       </c>
@@ -29049,9 +28866,6 @@
       <c r="O160" t="n">
         <v>9</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -29593,9 +29407,6 @@
       <c r="O163" t="n">
         <v>8</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.1538300016959758</v>
       </c>
@@ -30137,9 +29948,6 @@
       <c r="O166" t="n">
         <v>0</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0</v>
       </c>
@@ -30533,9 +30341,6 @@
       <c r="O168" t="n">
         <v>241</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.5095232161874976</v>
       </c>
@@ -30681,9 +30486,6 @@
       <c r="O169" t="n">
         <v>7</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.1542524990006642</v>
       </c>
@@ -31225,9 +31027,6 @@
       <c r="O172" t="n">
         <v>2</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.03845750042399394</v>
       </c>
@@ -31769,9 +31568,6 @@
       <c r="O175" t="n">
         <v>68</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.1437658867251031</v>
       </c>
@@ -31917,9 +31713,6 @@
       <c r="O176" t="n">
         <v>4</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.08814428514323666</v>
       </c>
@@ -32461,9 +32254,6 @@
       <c r="O179" t="n">
         <v>9</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.1730587519079727</v>
       </c>
@@ -33005,9 +32795,6 @@
       <c r="O182" t="n">
         <v>89</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.1881641752725614</v>
       </c>
@@ -33153,9 +32940,6 @@
       <c r="O183" t="n">
         <v>5</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0.1101803564290458</v>
       </c>
@@ -33697,9 +33481,6 @@
       <c r="O186" t="n">
         <v>7</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -34241,9 +34022,6 @@
       <c r="O189" t="n">
         <v>82</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.1733647457567419</v>
       </c>
@@ -34389,9 +34167,6 @@
       <c r="O190" t="n">
         <v>9</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -34933,9 +34708,6 @@
       <c r="O193" t="n">
         <v>3</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -35477,9 +35249,6 @@
       <c r="O196" t="n">
         <v>36</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.0761113517956428</v>
       </c>
@@ -35625,9 +35394,6 @@
       <c r="O197" t="n">
         <v>10</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -36169,9 +35935,6 @@
       <c r="O200" t="n">
         <v>7</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -36713,9 +36476,6 @@
       <c r="O203" t="n">
         <v>13</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.02748465481509323</v>
       </c>
@@ -36861,9 +36621,6 @@
       <c r="O204" t="n">
         <v>8</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -37405,9 +37162,6 @@
       <c r="O207" t="n">
         <v>9</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.1730587519079727</v>
       </c>
@@ -37949,9 +37703,6 @@
       <c r="O210" t="n">
         <v>11</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.02325624638200197</v>
       </c>
@@ -38097,9 +37848,6 @@
       <c r="O211" t="n">
         <v>10</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.2203607128580917</v>
       </c>
@@ -38641,9 +38389,6 @@
       <c r="O214" t="n">
         <v>7</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -39185,9 +38930,6 @@
       <c r="O217" t="n">
         <v>8</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.01691363373236507</v>
       </c>
@@ -39333,9 +39075,6 @@
       <c r="O218" t="n">
         <v>9</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -39877,9 +39616,6 @@
       <c r="O221" t="n">
         <v>8</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.1538300016959758</v>
       </c>
@@ -40421,9 +40157,6 @@
       <c r="O224" t="n">
         <v>9</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.0190278379489107</v>
       </c>
@@ -40569,9 +40302,6 @@
       <c r="O225" t="n">
         <v>17</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.3746132118587558</v>
       </c>
@@ -41113,9 +40843,6 @@
       <c r="O228" t="n">
         <v>7</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.1346012514839788</v>
       </c>
@@ -41657,9 +41384,6 @@
       <c r="O231" t="n">
         <v>4</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.008456816866182533</v>
       </c>
@@ -41805,9 +41529,6 @@
       <c r="O232" t="n">
         <v>18</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.396649283144565</v>
       </c>
@@ -42349,9 +42070,6 @@
       <c r="O235" t="n">
         <v>19</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.3653462540279425</v>
       </c>
@@ -42893,9 +42611,6 @@
       <c r="O238" t="n">
         <v>12</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.0253704505985476</v>
       </c>
@@ -43041,9 +42756,6 @@
       <c r="O239" t="n">
         <v>18</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.396649283144565</v>
       </c>
@@ -43585,9 +43297,6 @@
       <c r="O242" t="n">
         <v>3</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.05768625063599091</v>
       </c>
@@ -44129,9 +43838,6 @@
       <c r="O245" t="n">
         <v>194</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.4101556180098528</v>
       </c>
@@ -44277,9 +43983,6 @@
       <c r="O246" t="n">
         <v>8</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -44821,9 +44524,6 @@
       <c r="O249" t="n">
         <v>10</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.1918297779282576</v>
       </c>
@@ -45365,9 +45065,6 @@
       <c r="O252" t="n">
         <v>2</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.690595811536403</v>
       </c>
@@ -45761,9 +45458,6 @@
       <c r="O254" t="n">
         <v>188</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.395671517757322</v>
       </c>
@@ -45909,9 +45603,6 @@
       <c r="O255" t="n">
         <v>9</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -46615,9 +46306,6 @@
       <c r="O259" t="n">
         <v>9</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.1726468001354318</v>
       </c>
@@ -47159,9 +46847,6 @@
       <c r="O262" t="n">
         <v>50</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.1052317866375857</v>
       </c>
@@ -47307,9 +46992,6 @@
       <c r="O263" t="n">
         <v>7</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -48013,9 +47695,6 @@
       <c r="O267" t="n">
         <v>6</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -48557,9 +48236,6 @@
       <c r="O270" t="n">
         <v>84</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.1767894015511439</v>
       </c>
@@ -48705,9 +48381,6 @@
       <c r="O271" t="n">
         <v>7</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -49411,9 +49084,6 @@
       <c r="O275" t="n">
         <v>3</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -49955,9 +49625,6 @@
       <c r="O278" t="n">
         <v>267</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.5619377406447074</v>
       </c>
@@ -50103,9 +49770,6 @@
       <c r="O279" t="n">
         <v>10</v>
       </c>
-      <c r="Q279" t="n">
-        <v>0</v>
-      </c>
       <c r="R279" t="n">
         <v>0.2190739350432638</v>
       </c>
@@ -50809,9 +50473,6 @@
       <c r="O283" t="n">
         <v>5</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0.09591488896412878</v>
       </c>
@@ -51353,9 +51014,6 @@
       <c r="O286" t="n">
         <v>142</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0.2988582740507433</v>
       </c>
@@ -51501,9 +51159,6 @@
       <c r="O287" t="n">
         <v>7</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -52207,9 +51862,6 @@
       <c r="O291" t="n">
         <v>1</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -52751,9 +52403,6 @@
       <c r="O294" t="n">
         <v>126</v>
       </c>
-      <c r="Q294" t="n">
-        <v>0</v>
-      </c>
       <c r="R294" t="n">
         <v>0.2651841023267159</v>
       </c>
@@ -52899,9 +52548,6 @@
       <c r="O295" t="n">
         <v>9</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.1971665415389375</v>
       </c>
@@ -53605,9 +53251,6 @@
       <c r="O299" t="n">
         <v>3</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>0.05754893337847727</v>
       </c>
@@ -54149,9 +53792,6 @@
       <c r="O302" t="n">
         <v>67</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>0.1410105940943648</v>
       </c>
@@ -54297,9 +53937,6 @@
       <c r="O303" t="n">
         <v>7</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.1533517545302847</v>
       </c>
@@ -55003,9 +54640,6 @@
       <c r="O307" t="n">
         <v>1</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -55547,9 +55181,6 @@
       <c r="O310" t="n">
         <v>108</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0.227300659137185</v>
       </c>
@@ -55695,9 +55326,6 @@
       <c r="O311" t="n">
         <v>17</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -56401,9 +56029,6 @@
       <c r="O315" t="n">
         <v>6</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -56945,9 +56570,6 @@
       <c r="O318" t="n">
         <v>24</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0.05051125758604111</v>
       </c>
@@ -57093,9 +56715,6 @@
       <c r="O319" t="n">
         <v>6</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.1314443610259583</v>
       </c>
@@ -57799,9 +57418,6 @@
       <c r="O323" t="n">
         <v>6</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>0.1150978667569545</v>
       </c>
@@ -58343,9 +57959,6 @@
       <c r="O326" t="n">
         <v>17</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>0.03577880745677912</v>
       </c>
@@ -58491,9 +58104,6 @@
       <c r="O327" t="n">
         <v>22</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0.4819626570951804</v>
       </c>
@@ -59197,9 +58807,6 @@
       <c r="O331" t="n">
         <v>10</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>0.1918297779282576</v>
       </c>
@@ -59741,9 +59348,6 @@
       <c r="O334" t="n">
         <v>28</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.05892980051704796</v>
       </c>
@@ -59889,9 +59493,6 @@
       <c r="O335" t="n">
         <v>11</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -60595,9 +60196,6 @@
       <c r="O339" t="n">
         <v>9</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.1726468001354318</v>
       </c>
@@ -61139,9 +60737,6 @@
       <c r="O342" t="n">
         <v>16</v>
       </c>
-      <c r="Q342" t="n">
-        <v>0</v>
-      </c>
       <c r="R342" t="n">
         <v>0.03367417172402741</v>
       </c>
@@ -61287,9 +60882,6 @@
       <c r="O343" t="n">
         <v>17</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.3724256895735485</v>
       </c>
@@ -61993,9 +61585,6 @@
       <c r="O347" t="n">
         <v>9</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.1721450884710991</v>
       </c>
@@ -62537,9 +62126,6 @@
       <c r="O350" t="n">
         <v>3</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>1.02680473767706</v>
       </c>
@@ -62933,9 +62519,6 @@
       <c r="O352" t="n">
         <v>9</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.01886908139682484</v>
       </c>
@@ -63081,9 +62664,6 @@
       <c r="O353" t="n">
         <v>11</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>0.2395604718687949</v>
       </c>
@@ -63787,9 +63367,6 @@
       <c r="O357" t="n">
         <v>10</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0.1912723205234435</v>
       </c>
@@ -64331,9 +63908,6 @@
       <c r="O360" t="n">
         <v>8</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0.01677251679717764</v>
       </c>
@@ -64479,9 +64053,6 @@
       <c r="O361" t="n">
         <v>9</v>
       </c>
-      <c r="Q361" t="n">
-        <v>0</v>
-      </c>
       <c r="R361" t="n">
         <v>0.1960040224381049</v>
       </c>
@@ -65185,9 +64756,6 @@
       <c r="O365" t="n">
         <v>11</v>
       </c>
-      <c r="Q365" t="n">
-        <v>0</v>
-      </c>
       <c r="R365" t="n">
         <v>0.2103995525757878</v>
       </c>
@@ -65729,9 +65297,6 @@
       <c r="O368" t="n">
         <v>10</v>
       </c>
-      <c r="Q368" t="n">
-        <v>0</v>
-      </c>
       <c r="R368" t="n">
         <v>0.02096564599647205</v>
       </c>
@@ -65877,9 +65442,6 @@
       <c r="O369" t="n">
         <v>12</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.2613386965841399</v>
       </c>
@@ -66583,9 +66145,6 @@
       <c r="O373" t="n">
         <v>5</v>
       </c>
-      <c r="Q373" t="n">
-        <v>0</v>
-      </c>
       <c r="R373" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -67127,9 +66686,6 @@
       <c r="O376" t="n">
         <v>29</v>
       </c>
-      <c r="Q376" t="n">
-        <v>0</v>
-      </c>
       <c r="R376" t="n">
         <v>0.06080037338976894</v>
       </c>
@@ -67275,9 +66831,6 @@
       <c r="O377" t="n">
         <v>19</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.4137862695915548</v>
       </c>
@@ -67981,9 +67534,6 @@
       <c r="O381" t="n">
         <v>3</v>
       </c>
-      <c r="Q381" t="n">
-        <v>0</v>
-      </c>
       <c r="R381" t="n">
         <v>0.05738169615703305</v>
       </c>
@@ -68525,9 +68075,6 @@
       <c r="O384" t="n">
         <v>73</v>
       </c>
-      <c r="Q384" t="n">
-        <v>0</v>
-      </c>
       <c r="R384" t="n">
         <v>0.153049215774246</v>
       </c>
@@ -68673,9 +68220,6 @@
       <c r="O385" t="n">
         <v>12</v>
       </c>
-      <c r="Q385" t="n">
-        <v>0</v>
-      </c>
       <c r="R385" t="n">
         <v>0.2613386965841399</v>
       </c>
@@ -69379,9 +68923,6 @@
       <c r="O389" t="n">
         <v>7</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>0.1338906243664104</v>
       </c>
@@ -69923,9 +69464,6 @@
       <c r="O392" t="n">
         <v>4</v>
       </c>
-      <c r="Q392" t="n">
-        <v>0</v>
-      </c>
       <c r="R392" t="n">
         <v>0.008386258398588819</v>
       </c>
@@ -70071,9 +69609,6 @@
       <c r="O393" t="n">
         <v>7</v>
       </c>
-      <c r="Q393" t="n">
-        <v>0</v>
-      </c>
       <c r="R393" t="n">
         <v>0.152447573007415</v>
       </c>
@@ -70777,9 +70312,6 @@
       <c r="O397" t="n">
         <v>5</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>0.09563616026172174</v>
       </c>
@@ -71321,9 +70853,6 @@
       <c r="O400" t="n">
         <v>6</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0.01257938759788323</v>
       </c>
@@ -71469,9 +70998,6 @@
       <c r="O401" t="n">
         <v>8</v>
       </c>
-      <c r="Q401" t="n">
-        <v>0</v>
-      </c>
       <c r="R401" t="n">
         <v>0.17422579772276</v>
       </c>
@@ -72175,9 +71701,6 @@
       <c r="O405" t="n">
         <v>10</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>0.1912723205234435</v>
       </c>
@@ -72719,9 +72242,6 @@
       <c r="O408" t="n">
         <v>12</v>
       </c>
-      <c r="Q408" t="n">
-        <v>0</v>
-      </c>
       <c r="R408" t="n">
         <v>0.02515877519576646</v>
       </c>
@@ -72867,9 +72387,6 @@
       <c r="O409" t="n">
         <v>21</v>
       </c>
-      <c r="Q409" t="n">
-        <v>0</v>
-      </c>
       <c r="R409" t="n">
         <v>0.4573427190222448</v>
       </c>
@@ -73573,9 +73090,6 @@
       <c r="O413" t="n">
         <v>7</v>
       </c>
-      <c r="Q413" t="n">
-        <v>0</v>
-      </c>
       <c r="R413" t="n">
         <v>0.1338906243664104</v>
       </c>
@@ -74117,9 +73631,6 @@
       <c r="O416" t="n">
         <v>2</v>
       </c>
-      <c r="Q416" t="n">
-        <v>0</v>
-      </c>
       <c r="R416" t="n">
         <v>0.004193129199294409</v>
       </c>
@@ -74265,9 +73776,6 @@
       <c r="O417" t="n">
         <v>13</v>
       </c>
-      <c r="Q417" t="n">
-        <v>0</v>
-      </c>
       <c r="R417" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -74971,9 +74479,6 @@
       <c r="O421" t="n">
         <v>6</v>
       </c>
-      <c r="Q421" t="n">
-        <v>0</v>
-      </c>
       <c r="R421" t="n">
         <v>0.1147633923140661</v>
       </c>
@@ -75515,9 +75020,6 @@
       <c r="O424" t="n">
         <v>9</v>
       </c>
-      <c r="Q424" t="n">
-        <v>0</v>
-      </c>
       <c r="R424" t="n">
         <v>0.01886908139682484</v>
       </c>
@@ -75663,9 +75165,6 @@
       <c r="O425" t="n">
         <v>12</v>
       </c>
-      <c r="Q425" t="n">
-        <v>0</v>
-      </c>
       <c r="R425" t="n">
         <v>0.2613386965841399</v>
       </c>
@@ -76369,9 +75868,6 @@
       <c r="O429" t="n">
         <v>16</v>
       </c>
-      <c r="Q429" t="n">
-        <v>0</v>
-      </c>
       <c r="R429" t="n">
         <v>0.3060357128375096</v>
       </c>
@@ -76913,9 +76409,6 @@
       <c r="O432" t="n">
         <v>135</v>
       </c>
-      <c r="Q432" t="n">
-        <v>0</v>
-      </c>
       <c r="R432" t="n">
         <v>0.2830362209523726</v>
       </c>
@@ -77061,9 +76554,6 @@
       <c r="O433" t="n">
         <v>17</v>
       </c>
-      <c r="Q433" t="n">
-        <v>0</v>
-      </c>
       <c r="R433" t="n">
         <v>0.3702298201608649</v>
       </c>
@@ -77767,9 +77257,6 @@
       <c r="O437" t="n">
         <v>23</v>
       </c>
-      <c r="Q437" t="n">
-        <v>0</v>
-      </c>
       <c r="R437" t="n">
         <v>0.43992633720392</v>
       </c>
@@ -78311,9 +77798,6 @@
       <c r="O440" t="n">
         <v>190</v>
       </c>
-      <c r="Q440" t="n">
-        <v>0</v>
-      </c>
       <c r="R440" t="n">
         <v>0.3983472739329689</v>
       </c>
@@ -78458,9 +77942,6 @@
       </c>
       <c r="O441" t="n">
         <v>14</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>0</v>
       </c>
       <c r="R441" t="n">
         <v>0.3048951460148299</v>
